--- a/samples/sample_douyin_period2.xlsx
+++ b/samples/sample_douyin_period2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="80">
   <si>
     <t>视频标题</t>
   </si>
@@ -46,220 +46,211 @@
     <t>平均播放时长(秒)</t>
   </si>
   <si>
-    <t>网吧五连坐｜vlog</t>
-  </si>
-  <si>
-    <t>2026-08-02 07:30:00</t>
-  </si>
-  <si>
-    <t>2155</t>
-  </si>
-  <si>
-    <t>宿舍开箱（上集）</t>
-  </si>
-  <si>
-    <t>2026-08-02 20:10:00</t>
+    <t>图书馆占座！</t>
+  </si>
+  <si>
+    <t>2026-07-04 20:05:00</t>
+  </si>
+  <si>
+    <t>2.6万</t>
+  </si>
+  <si>
+    <t>食堂测评（上集）</t>
+  </si>
+  <si>
+    <t>2026-07-04 22:45:00</t>
+  </si>
+  <si>
+    <t>3.8万</t>
+  </si>
+  <si>
+    <t>食堂测评！</t>
+  </si>
+  <si>
+    <t>2026-08-04 22:05:00</t>
+  </si>
+  <si>
+    <t>7251</t>
+  </si>
+  <si>
+    <t>图书馆占座（上集）</t>
+  </si>
+  <si>
+    <t>2026-08-05 16:15:00</t>
+  </si>
+  <si>
+    <t>4150</t>
+  </si>
+  <si>
+    <t>宿舍做饭</t>
+  </si>
+  <si>
+    <t>2026-08-05 19:05:00</t>
+  </si>
+  <si>
+    <t>1.8万</t>
+  </si>
+  <si>
+    <t>社团招新｜vlog</t>
+  </si>
+  <si>
+    <t>2026-08-05 22:15:00</t>
+  </si>
+  <si>
+    <t>1.6万</t>
+  </si>
+  <si>
+    <t>宿舍做饭#校园生活</t>
+  </si>
+  <si>
+    <t>2026-07-06 21:05:00</t>
+  </si>
+  <si>
+    <t>2.0万</t>
+  </si>
+  <si>
+    <t>期末复习｜vlog</t>
+  </si>
+  <si>
+    <t>2026-07-07 23:30:00</t>
+  </si>
+  <si>
+    <t>1.1万</t>
+  </si>
+  <si>
+    <t>食堂测评｜vlog</t>
+  </si>
+  <si>
+    <t>2026-07-08 18:15:00</t>
   </si>
   <si>
     <t>1.2万</t>
   </si>
   <si>
-    <t>图书馆占座（下集）</t>
-  </si>
-  <si>
-    <t>2026-08-04 22:00:00</t>
-  </si>
-  <si>
-    <t>2.4万</t>
-  </si>
-  <si>
-    <t>宿舍做饭</t>
-  </si>
-  <si>
-    <t>2026-08-05 19:05:00</t>
-  </si>
-  <si>
-    <t>1.8万</t>
-  </si>
-  <si>
-    <t>宿舍开箱</t>
-  </si>
-  <si>
-    <t>2026-08-07 09:45:00</t>
-  </si>
-  <si>
-    <t>5704</t>
+    <t>宿舍开箱｜vlog</t>
+  </si>
+  <si>
+    <t>2026-07-08 21:05:00</t>
+  </si>
+  <si>
+    <t>3.6万</t>
+  </si>
+  <si>
+    <t>军训回忆（上集）</t>
+  </si>
+  <si>
+    <t>2026-07-09 18:10:00</t>
+  </si>
+  <si>
+    <t>1.0万</t>
+  </si>
+  <si>
+    <t>图书馆占座#校园生活</t>
+  </si>
+  <si>
+    <t>2026-08-09 22:15:00</t>
+  </si>
+  <si>
+    <t>宿舍做饭（下集）</t>
+  </si>
+  <si>
+    <t>2026-07-11 16:05:00</t>
+  </si>
+  <si>
+    <t>校园夜跑（上集）</t>
+  </si>
+  <si>
+    <t>2026-07-13 13:15:00</t>
+  </si>
+  <si>
+    <t>2026-08-14 13:10:00</t>
+  </si>
+  <si>
+    <t>6429</t>
+  </si>
+  <si>
+    <t>2026-07-15 18:05:00</t>
+  </si>
+  <si>
+    <t>3433</t>
   </si>
   <si>
     <t>社团招新</t>
   </si>
   <si>
-    <t>2026-08-07 21:30:00</t>
-  </si>
-  <si>
-    <t>8853</t>
-  </si>
-  <si>
-    <t>军训回忆｜vlog</t>
-  </si>
-  <si>
-    <t>2026-08-08 09:15:00</t>
-  </si>
-  <si>
-    <t>5682</t>
-  </si>
-  <si>
-    <t>宿舍做饭（下集）</t>
-  </si>
-  <si>
-    <t>2026-08-08 09:05:00</t>
-  </si>
-  <si>
-    <t>7839</t>
-  </si>
-  <si>
-    <t>考研日常</t>
-  </si>
-  <si>
-    <t>2026-08-09 20:05:00</t>
-  </si>
-  <si>
-    <t>图书馆占座#校园生活</t>
-  </si>
-  <si>
-    <t>2026-08-09 22:15:00</t>
-  </si>
-  <si>
-    <t>2.6万</t>
-  </si>
-  <si>
-    <t>考研日常（上集）</t>
-  </si>
-  <si>
-    <t>2026-08-10 12:15:00</t>
-  </si>
-  <si>
-    <t>1.1万</t>
-  </si>
-  <si>
-    <t>考研日常#校园生活</t>
-  </si>
-  <si>
-    <t>2026-08-12 22:45:00</t>
-  </si>
-  <si>
-    <t>操场日落｜vlog</t>
-  </si>
-  <si>
-    <t>2026-08-13 15:30:00</t>
-  </si>
-  <si>
-    <t>6569</t>
-  </si>
-  <si>
-    <t>军训回忆#校园生活</t>
-  </si>
-  <si>
-    <t>2026-08-14 19:00:00</t>
-  </si>
-  <si>
-    <t>14.1万</t>
-  </si>
-  <si>
-    <t>2026-08-14 22:05:00</t>
-  </si>
-  <si>
-    <t>5845</t>
-  </si>
-  <si>
-    <t>食堂测评！</t>
-  </si>
-  <si>
-    <t>2026-08-15 13:30:00</t>
-  </si>
-  <si>
-    <t>6048</t>
-  </si>
-  <si>
-    <t>早八日常（下集）</t>
-  </si>
-  <si>
-    <t>2026-08-19 16:00:00</t>
-  </si>
-  <si>
-    <t>7008</t>
-  </si>
-  <si>
-    <t>早八日常#校园生活</t>
-  </si>
-  <si>
-    <t>2026-08-19 22:10:00</t>
+    <t>2026-07-16 11:10:00</t>
+  </si>
+  <si>
+    <t>4211</t>
+  </si>
+  <si>
+    <t>网吧五连坐</t>
+  </si>
+  <si>
+    <t>2026-07-16 23:45:00</t>
+  </si>
+  <si>
+    <t>网吧五连坐（下集）</t>
+  </si>
+  <si>
+    <t>2026-07-17 19:10:00</t>
+  </si>
+  <si>
+    <t>1.4万</t>
+  </si>
+  <si>
+    <t>期末复习</t>
+  </si>
+  <si>
+    <t>2026-07-21 11:00:00</t>
+  </si>
+  <si>
+    <t>校园夜跑</t>
+  </si>
+  <si>
+    <t>2026-08-21 15:10:00</t>
+  </si>
+  <si>
+    <t>2491</t>
+  </si>
+  <si>
+    <t>操场日落（上集）</t>
+  </si>
+  <si>
+    <t>2026-08-21 23:05:00</t>
+  </si>
+  <si>
+    <t>8189</t>
+  </si>
+  <si>
+    <t>2026-08-22 08:15:00</t>
+  </si>
+  <si>
+    <t>5102</t>
+  </si>
+  <si>
+    <t>军训回忆</t>
+  </si>
+  <si>
+    <t>2026-07-22 21:15:00</t>
+  </si>
+  <si>
+    <t>2.1万</t>
   </si>
   <si>
     <t>早八日常</t>
   </si>
   <si>
-    <t>2026-08-20 11:45:00</t>
-  </si>
-  <si>
-    <t>6472</t>
-  </si>
-  <si>
-    <t>2026-08-20 17:10:00</t>
-  </si>
-  <si>
-    <t>3093</t>
-  </si>
-  <si>
-    <t>宿舍做饭（上集）</t>
-  </si>
-  <si>
-    <t>2026-08-21 08:05:00</t>
-  </si>
-  <si>
-    <t>4.8万</t>
-  </si>
-  <si>
-    <t>2026-08-21 21:45:00</t>
-  </si>
-  <si>
-    <t>1.6万</t>
-  </si>
-  <si>
-    <t>网吧五连坐#校园生活</t>
-  </si>
-  <si>
-    <t>2026-08-25 17:10:00</t>
-  </si>
-  <si>
-    <t>3793</t>
-  </si>
-  <si>
-    <t>社团招新！</t>
-  </si>
-  <si>
-    <t>2026-08-26 12:45:00</t>
-  </si>
-  <si>
-    <t>8043</t>
-  </si>
-  <si>
-    <t>军训回忆</t>
-  </si>
-  <si>
-    <t>2026-08-26 16:00:00</t>
-  </si>
-  <si>
-    <t>2727</t>
-  </si>
-  <si>
-    <t>考研日常！</t>
-  </si>
-  <si>
-    <t>2026-08-26 16:10:00</t>
-  </si>
-  <si>
-    <t>2904</t>
+    <t>2026-07-23 07:30:00</t>
+  </si>
+  <si>
+    <t>2695</t>
+  </si>
+  <si>
+    <t>2026-08-25 17:15:00</t>
+  </si>
+  <si>
+    <t>1.9万</t>
   </si>
 </sst>
 </file>
@@ -686,31 +677,31 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
       </c>
       <c r="E2">
-        <v>126</v>
+        <v>936</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>254</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="H2">
-        <v>14</v>
+        <v>319</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>118</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K2">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -721,31 +712,31 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3">
-        <v>387</v>
+        <v>1979</v>
       </c>
       <c r="F3">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="H3">
-        <v>176</v>
+        <v>285</v>
       </c>
       <c r="I3">
+        <v>37</v>
+      </c>
+      <c r="J3">
         <v>38</v>
       </c>
-      <c r="J3">
-        <v>41</v>
-      </c>
       <c r="K3">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -756,31 +747,31 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
       </c>
       <c r="E4">
-        <v>1459</v>
+        <v>428</v>
       </c>
       <c r="F4">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H4">
-        <v>295</v>
+        <v>47</v>
       </c>
       <c r="I4">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="J4">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="K4">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -791,31 +782,31 @@
         <v>21</v>
       </c>
       <c r="C5">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
       </c>
       <c r="E5">
-        <v>774</v>
+        <v>247</v>
       </c>
       <c r="F5">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="H5">
-        <v>253</v>
+        <v>39</v>
       </c>
       <c r="I5">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K5">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -826,31 +817,31 @@
         <v>24</v>
       </c>
       <c r="C6">
-        <v>99</v>
+        <v>158</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
       </c>
       <c r="E6">
-        <v>172</v>
+        <v>774</v>
       </c>
       <c r="F6">
+        <v>103</v>
+      </c>
+      <c r="G6">
+        <v>114</v>
+      </c>
+      <c r="H6">
+        <v>253</v>
+      </c>
+      <c r="I6">
+        <v>57</v>
+      </c>
+      <c r="J6">
+        <v>40</v>
+      </c>
+      <c r="K6">
         <v>68</v>
-      </c>
-      <c r="G6">
-        <v>27</v>
-      </c>
-      <c r="H6">
-        <v>78</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>37</v>
-      </c>
-      <c r="K6">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -861,31 +852,31 @@
         <v>27</v>
       </c>
       <c r="C7">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
       </c>
       <c r="E7">
-        <v>610</v>
+        <v>645</v>
       </c>
       <c r="F7">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="G7">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="H7">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="I7">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K7">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -896,31 +887,31 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
         <v>31</v>
       </c>
       <c r="E8">
-        <v>303</v>
+        <v>1363</v>
       </c>
       <c r="F8">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="G8">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="H8">
-        <v>46</v>
+        <v>231</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="J8">
         <v>49</v>
       </c>
       <c r="K8">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -931,31 +922,31 @@
         <v>33</v>
       </c>
       <c r="C9">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
         <v>34</v>
       </c>
       <c r="E9">
-        <v>291</v>
+        <v>410</v>
       </c>
       <c r="F9">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="G9">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H9">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="I9">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="K9">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -966,171 +957,171 @@
         <v>36</v>
       </c>
       <c r="C10">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E10">
-        <v>1211</v>
+        <v>380</v>
       </c>
       <c r="F10">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="G10">
-        <v>200</v>
+        <v>86</v>
       </c>
       <c r="H10">
-        <v>212</v>
+        <v>107</v>
       </c>
       <c r="I10">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="J10">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="K10">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>1427</v>
+        <v>2067</v>
       </c>
       <c r="F11">
-        <v>171</v>
+        <v>366</v>
       </c>
       <c r="G11">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="H11">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="I11">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="J11">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="K11">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12">
+        <v>574</v>
+      </c>
+      <c r="F12">
+        <v>127</v>
+      </c>
+      <c r="G12">
+        <v>70</v>
+      </c>
+      <c r="H12">
+        <v>116</v>
+      </c>
+      <c r="I12">
         <v>41</v>
       </c>
-      <c r="C12">
-        <v>83</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12">
-        <v>490</v>
-      </c>
-      <c r="F12">
-        <v>86</v>
-      </c>
-      <c r="G12">
-        <v>42</v>
-      </c>
-      <c r="H12">
-        <v>78</v>
-      </c>
-      <c r="I12">
-        <v>31</v>
-      </c>
       <c r="J12">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="K12">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E13">
-        <v>450</v>
+        <v>1427</v>
       </c>
       <c r="F13">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="G13">
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="H13">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="I13">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="J13">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K13">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E14">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G14">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H14">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="I14">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="J14">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="K14">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1141,203 +1132,203 @@
         <v>49</v>
       </c>
       <c r="C15">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15">
+        <v>410</v>
+      </c>
+      <c r="F15">
+        <v>109</v>
+      </c>
+      <c r="G15">
         <v>50</v>
       </c>
-      <c r="E15">
-        <v>9840</v>
-      </c>
-      <c r="F15">
-        <v>887</v>
-      </c>
-      <c r="G15">
-        <v>1093</v>
-      </c>
       <c r="H15">
-        <v>1005</v>
+        <v>216</v>
       </c>
       <c r="I15">
-        <v>533</v>
+        <v>66</v>
       </c>
       <c r="J15">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="K15">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16">
+        <v>132</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16">
+        <v>354</v>
+      </c>
+      <c r="F16">
+        <v>46</v>
+      </c>
+      <c r="G16">
+        <v>39</v>
+      </c>
+      <c r="H16">
+        <v>41</v>
+      </c>
+      <c r="I16">
+        <v>11</v>
+      </c>
+      <c r="J16">
         <v>40</v>
       </c>
-      <c r="B16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16">
-        <v>40</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16">
-        <v>361</v>
-      </c>
-      <c r="F16">
-        <v>29</v>
-      </c>
-      <c r="G16">
-        <v>49</v>
-      </c>
-      <c r="H16">
-        <v>72</v>
-      </c>
-      <c r="I16">
-        <v>17</v>
-      </c>
-      <c r="J16">
-        <v>51</v>
-      </c>
       <c r="K16">
-        <v>18</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17">
+        <v>214</v>
+      </c>
+      <c r="D17" t="s">
         <v>53</v>
       </c>
-      <c r="B17" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
-      </c>
       <c r="E17">
-        <v>331</v>
+        <v>167</v>
       </c>
       <c r="F17">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="G17">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H17">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="J17">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="K17">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18">
+        <v>139</v>
+      </c>
+      <c r="D18" t="s">
         <v>56</v>
       </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18">
+      <c r="E18">
+        <v>336</v>
+      </c>
+      <c r="F18">
+        <v>33</v>
+      </c>
+      <c r="G18">
+        <v>17</v>
+      </c>
+      <c r="H18">
         <v>49</v>
       </c>
-      <c r="D18" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18">
-        <v>225</v>
-      </c>
-      <c r="F18">
-        <v>68</v>
-      </c>
-      <c r="G18">
-        <v>36</v>
-      </c>
-      <c r="H18">
-        <v>105</v>
-      </c>
       <c r="I18">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="J18">
         <v>44</v>
       </c>
       <c r="K18">
-        <v>26</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C19">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E19">
-        <v>591</v>
+        <v>286</v>
       </c>
       <c r="F19">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G19">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H19">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="I19">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="J19">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K19">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
         <v>61</v>
       </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20">
-        <v>46</v>
-      </c>
-      <c r="D20" t="s">
-        <v>63</v>
-      </c>
       <c r="E20">
-        <v>313</v>
+        <v>448</v>
       </c>
       <c r="F20">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="G20">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="H20">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="I20">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="J20">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="K20">
         <v>25</v>
@@ -1345,247 +1336,247 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="E21">
-        <v>165</v>
+        <v>586</v>
       </c>
       <c r="F21">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="G21">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="H21">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="J21">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K21">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22">
+        <v>238</v>
+      </c>
+      <c r="D22" t="s">
         <v>66</v>
       </c>
-      <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22">
-        <v>237</v>
-      </c>
-      <c r="D22" t="s">
-        <v>68</v>
-      </c>
       <c r="E22">
-        <v>1742</v>
+        <v>101</v>
       </c>
       <c r="F22">
-        <v>493</v>
+        <v>22</v>
       </c>
       <c r="G22">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="H22">
-        <v>640</v>
+        <v>26</v>
       </c>
       <c r="I22">
-        <v>148</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K22">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23">
+        <v>216</v>
+      </c>
+      <c r="D23" t="s">
         <v>69</v>
       </c>
-      <c r="C23">
-        <v>135</v>
-      </c>
-      <c r="D23" t="s">
-        <v>70</v>
-      </c>
       <c r="E23">
-        <v>641</v>
+        <v>383</v>
       </c>
       <c r="F23">
-        <v>187</v>
+        <v>68</v>
       </c>
       <c r="G23">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="H23">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="I23">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="J23">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="K23">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24">
+        <v>119</v>
+      </c>
+      <c r="D24" t="s">
         <v>71</v>
       </c>
-      <c r="B24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24">
-        <v>185</v>
-      </c>
-      <c r="D24" t="s">
-        <v>73</v>
-      </c>
       <c r="E24">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="F24">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G24">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H24">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K24">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25">
+        <v>227</v>
+      </c>
+      <c r="D25" t="s">
         <v>74</v>
       </c>
-      <c r="B25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25">
-        <v>234</v>
-      </c>
-      <c r="D25" t="s">
-        <v>76</v>
-      </c>
       <c r="E25">
-        <v>415</v>
+        <v>874</v>
       </c>
       <c r="F25">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="G25">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="H25">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="I25">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="J25">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K25">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26">
+        <v>172</v>
+      </c>
+      <c r="D26" t="s">
         <v>77</v>
       </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26">
-        <v>81</v>
-      </c>
-      <c r="D26" t="s">
-        <v>79</v>
-      </c>
       <c r="E26">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="F26">
+        <v>19</v>
+      </c>
+      <c r="G26">
         <v>12</v>
       </c>
-      <c r="G26">
-        <v>15</v>
-      </c>
       <c r="H26">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J26">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="K26">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27">
         <v>81</v>
       </c>
-      <c r="C27">
-        <v>82</v>
-      </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E27">
-        <v>191</v>
+        <v>814</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="G27">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="H27">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J27">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="K27">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
